--- a/output/full_scan/batch_seq2_2026-05-23.xlsx
+++ b/output/full_scan/batch_seq2_2026-05-23.xlsx
@@ -88924,7 +88924,7 @@
         <v>52.5</v>
       </c>
       <c r="AC310" t="n">
-        <v>1.928122340488506</v>
+        <v>1.928122340488505</v>
       </c>
       <c r="AD310" t="n">
         <v>55.57019788283333</v>
